--- a/nyc_taxi_analysis/05_vlm_reasoning/vlm_reasoning.xlsx
+++ b/nyc_taxi_analysis/05_vlm_reasoning/vlm_reasoning.xlsx
@@ -431,13 +431,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
@@ -449,7 +449,7 @@
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="17" customWidth="1" min="19" max="19"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>(average_speed_mph / trip_distance)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -605,37 +605,37 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive correlation between fare_amount and total_amount with Pearson r = +0.9657 and Spearman rho = +0.9571. The OLS slope is +1.1631 per unit of fare_amount, indicating a strong linear relationship.</t>
+          <t>The relationship between average_speed_mph_per_trip_distance and total_amount is very strong and negative, with a Pearson r of -0.4255 and a Spearman rho of -0.8885. The functional form is inverse, with an R^2 of 0.975, indicating a nonlinear relationship. As average speed increases, the total amount decreases, but the rate of decrease flattens out at higher speeds.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the fare_amount, which is a component of the total_amount.</t>
+          <t>Higher average speeds are associated with lower total amounts for taxi trips, possibly due to shorter trip durations at higher speeds.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>fare_amount is a component of total_amount, leading to a mechanical correlation.</t>
+          <t>Higher speeds may lead to shorter trip durations, reducing the total fare.; Traffic congestion at lower speeds could increase trip duration and fare.</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>None, as this is a mechanical relationship due to accounting identity.</t>
+          <t>Trips with higher speeds might be longer distances with fewer stops, leading to lower per-mile costs.</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>None, as the relationship is mechanical.</t>
+          <t>Trip distance; Traffic conditions; Time of day</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -645,11 +645,11 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="Q2" t="b">
         <v>1</v>
@@ -662,17 +662,17 @@
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>note:accounting_identity_correctly_labelled; note:filters_not_disclosed</t>
+          <t>note:hedged_causal_language; note:filters_not_disclosed; note:semantically_surprising</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>2207</v>
+        <v>2472</v>
       </c>
       <c r="V2" t="n">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="W2" t="n">
-        <v>2.434</v>
+        <v>2.485</v>
       </c>
     </row>
     <row r="3">
@@ -681,7 +681,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(trip_distance * trip_duration_minutes)</t>
+          <t>trip_distance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -704,27 +704,27 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_distance_times_trip_duration_minutes and total_amount, with a Pearson correlation of +0.7413 and a Spearman rho of +0.8954 over 3,509,466 rows. The OLS slope is +0.061397 per unit of trip_distance_times_trip_duration_minutes.</t>
+          <t>The statistics show a very strong positive association between trip_distance and total_amount, with a Pearson correlation of +0.8674 and a Spearman rho of +0.8474. The OLS slope is +4.2311 per unit of trip_distance, and the functional form fitted to the conditional mean is linear with an R^2 of 0.993. The mean total_amount increases from 17.15 to 90.55 as trip_distance increases.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the product of trip distance and trip duration. Longer and/or longer-duration trips generally result in higher fares.</t>
+          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the trip distance. As the trip distance increases, the total amount charged also increases.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Longer trips naturally incur higher costs due to increased distance and time.; Taxi fare structures often include components that scale with distance and time.</t>
+          <t>Longer trips naturally incur higher costs due to increased time and distance traveled.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>The association may partly reflect fare components like tolls and surcharges that increase with trip length.</t>
+          <t>The correlation might be influenced by other fare components that increase with distance.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Trip distance and duration are directly related to fare amount due to fare calculation methods.</t>
+          <t>Fare components such as tolls, surcharges, and taxes that are distance-dependent.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>2162</v>
+        <v>2311</v>
       </c>
       <c r="V3" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="W3" t="n">
-        <v>2.301</v>
+        <v>3.238</v>
       </c>
     </row>
     <row r="4">
@@ -780,7 +780,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>trip_duration_minutes</t>
+          <t>log(trip_distance)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -803,27 +803,27 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_duration_minutes and total_amount, with a Pearson correlation of +0.6988 and a Spearman rho of +0.8885. The OLS slope is +1.0388 per unit of trip_duration_minutes. The hexbin plot illustrates this relationship with a dense clustering along the line of best fit.</t>
+          <t>The statistics show a very strong positive association between log_trip_distance and total_amount, with a Pearson correlation of +0.7002 and a Spearman rho of +0.8474. The relationship is materially nonlinear, with a quadratic fit achieving R^2 = 0.977 on the conditional mean, indicating a strong fit. The OLS slope is +14.071 per unit of log_trip_distance.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Longer trip durations are associated with higher total amounts charged to passengers.</t>
+          <t>As the log of trip distance increases, the total amount charged to passengers tends to increase significantly.</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Longer trips naturally incur higher fares due to increased distance and time, which are key components of taxi fare calculations.</t>
+          <t>Longer trips naturally incur higher fares due to increased distance traveled.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>The relationship could be influenced by additional charges such as tolls and surcharges that increase with trip duration.</t>
+          <t>The relationship could be influenced by other fare components that increase with distance.</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Trip distance, as longer durations often correlate with longer distances, which directly affect the fare.</t>
+          <t>Fare components like tolls, surcharges, and taxes that are distance-dependent.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
@@ -864,13 +864,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>2128</v>
+        <v>2430</v>
       </c>
       <c r="V4" t="n">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="W4" t="n">
-        <v>2.201</v>
+        <v>2.512</v>
       </c>
     </row>
     <row r="5">
@@ -879,7 +879,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>trip_distance</t>
+          <t>(trip_distance / passenger_count)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -902,27 +902,27 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_distance and total_amount, with a Pearson correlation of +0.8674 and a Spearman rho of +0.8474. The OLS slope is +4.2311 per unit of trip_distance.</t>
+          <t>The statistics show a very strong positive association between trip_distance_per_passenger_count and total_amount, with a Pearson correlation of +0.8452 and Spearman rho of +0.8337. The fitted linear model suggests that for each unit increase in trip_distance_per_passenger_count, the total_amount increases by approximately 4.571 USD. The conditional mean of total_amount rises from 14.73 to 88.56 USD as trip_distance_per_passenger_count increases.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the distance traveled. As the trip distance increases, the total amount charged also increases.</t>
+          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the trip distance per passenger count. As the distance per passenger increases, the total fare tends to increase.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Longer trips naturally incur higher costs due to increased time and fuel consumption.</t>
+          <t>Longer trips naturally incur higher fares due to distance-based pricing.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>The correlation is partly mechanical because total_amount is the sum of fare components, which are likely distance-dependent.</t>
+          <t>Trips with more passengers may have additional charges or fees.</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Trip duration; Traffic conditions; Surcharges such as tolls and congestion fees</t>
+          <t>Other fare components like tolls and surcharges that are mechanically included in the total_amount.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -942,11 +942,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
@@ -955,21 +955,21 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>note:filters_not_disclosed</t>
+          <t>warning:causal_claim_from_association; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>2134</v>
+        <v>2325</v>
       </c>
       <c r="V5" t="n">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="W5" t="n">
-        <v>1.93</v>
+        <v>3.181</v>
       </c>
     </row>
     <row r="6">
@@ -978,7 +978,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(fare_amount / trip_distance)</t>
+          <t>(passenger_count * trip_distance)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -1001,27 +1001,27 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>The relationship between fare_amount/trip_distance and total_amount shows a weak positive linear association (Pearson r = +0.0405) and a moderate negative monotonic association (Spearman rho = -0.4523). The normalized mutual information is 0.0677, indicating a weak association.</t>
+          <t>The relationship between passenger_count_times_trip_distance and total_amount shows a very strong positive association, with a Pearson correlation of +0.7807 and a Spearman rho of +0.8348. The OLS slope is +2.3402, indicating that for each unit increase in passenger_count_times_trip_distance, the total_amount increases by approximately $2.34. The functional form is linear with an R^2 of 0.977 on the conditional mean.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>The fare per mile is weakly associated with the total amount paid, suggesting that other factors may influence the total fare more strongly.</t>
+          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the product of passenger count and trip distance. As this product increases, the total fare also increases.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Higher fare rates per mile could lead to higher total fares.; Nonlinear pricing structures or additional fees may affect the total amount.</t>
+          <t>Longer trips with more passengers likely incur higher fares due to increased distance and potential surcharges.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>The relationship might be influenced by nonlinear pricing or additional charges not captured by fare_amount/trip_distance.</t>
+          <t>The correlation may be partly due to the mechanical relationship between trip distance and fare components.</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Trip distance; Additional fees and surcharges</t>
+          <t>Trip duration, traffic conditions, and additional surcharges could also influence the total fare.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>very strong</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.5499999999999999</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
@@ -1054,21 +1054,21 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>note:hedged_causal_language; warning:accounting_identity_presented_as_discovery; note:filters_not_disclosed</t>
+          <t>note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>2142</v>
+        <v>2373</v>
       </c>
       <c r="V6" t="n">
-        <v>268</v>
+        <v>301</v>
       </c>
       <c r="W6" t="n">
-        <v>2.467</v>
+        <v>2.825</v>
       </c>
     </row>
     <row r="7">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>log(trip_distance)</t>
+          <t>(average_speed_mph * trip_distance)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E7" t="b">
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between log_trip_distance and total_amount, with a Pearson correlation of +0.7002 and a Spearman rho of +0.8474. The OLS slope is +14.071 per unit of log_trip_distance.</t>
+          <t>The relationship between total_amount and average_speed_mph_times_trip_distance is strong and positive, with a Pearson correlation of +0.7788 and a Spearman rho of +0.7263. The quadratic fit shows an R^2 of 0.988, indicating a strong nonlinear relationship. The total_amount increases with average_speed_mph_times_trip_distance, with the mean of total_amount rising from 19.63 to 86.12 USD as average_speed_mph_times_trip_distance increases.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>As the log of trip distance increases, the total amount charged to passengers tends to increase.</t>
+          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the product of average speed and trip distance, suggesting that longer and faster trips tend to result in higher fares.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Longer trips naturally incur higher fares due to increased distance.</t>
+          <t>Longer distances and higher speeds may lead to higher fares due to increased time and distance charges.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>The relationship is partly mechanical since total_amount is the sum of fare components, which are distance-dependent.</t>
+          <t>The relationship might be influenced by other fare components that are mechanically related to total_amount.</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Other fare components like tolls and surcharges that vary with distance.</t>
+          <t>Fare components such as tolls and surcharges that are part of total_amount.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1135,16 +1135,16 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>very strong</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
@@ -1157,17 +1157,17 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>note:filters_not_disclosed</t>
+          <t>note:hedged_causal_language; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>2122</v>
+        <v>2386</v>
       </c>
       <c r="V7" t="n">
-        <v>228</v>
+        <v>309</v>
       </c>
       <c r="W7" t="n">
-        <v>2.154</v>
+        <v>3.242</v>
       </c>
     </row>
     <row r="8">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(trip_distance / trip_duration_minutes)</t>
+          <t>(fare_per_mile * trip_distance)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a positive association between trip_distance_per_trip_duration_minutes and total_amount with a Pearson correlation of +0.5474 and a Spearman rho of +0.3531. The OLS slope is +104.1 per unit of trip_distance_per_trip_duration_minutes.</t>
+          <t>The total amount charged to passengers is very strongly associated with fare_per_mile_times_trip_distance, with a Pearson correlation of +0.9657 and Spearman rho of +0.9571 over 3,509,466 rows. The relationship is positive and linear, with the conditional mean of total_amount increasing from 11.86 to 96.17 as fare_per_mile_times_trip_distance increases.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>As the trip distance per trip duration increases, the total amount charged to passengers tends to increase.</t>
+          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the fare per mile times the trip distance.</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Longer trips or faster trips may result in higher fares due to increased distance covered in a given time.</t>
+          <t>The total amount is likely calculated based on the fare per mile and the distance traveled.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>The correlation might be partly due to the mechanical relationship between total_amount and its components.</t>
+          <t>The relationship is mechanical due to total_amount being a sum of fare components.</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Trip distance and duration, as they directly influence fare calculations.</t>
+          <t>None, as the relationship is mechanical.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>very strong</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
@@ -1256,17 +1256,17 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>note:filters_not_disclosed</t>
+          <t>note:accounting_identity_correctly_labelled; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>2101</v>
+        <v>2398</v>
       </c>
       <c r="V8" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="W8" t="n">
-        <v>2.105</v>
+        <v>2.189</v>
       </c>
     </row>
     <row r="9">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>(trip_duration_minutes / trip_distance)</t>
+          <t>log1p(trip_distance)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -1298,27 +1298,27 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>The relationship between trip_duration_minutes_per_trip_distance and total_amount shows a weak positive linear association (Pearson r = +0.0261) and a moderate negative monotonic association (Spearman rho = -0.3531). The normalized mutual information is 0.0492, indicating low shared information. The OLS slope is +0.003692, suggesting a slight increase in total_amount with trip_duration_minutes_per_trip_distance.</t>
+          <t>The statistics show a very strong positive association between log1p_trip_distance and total_amount, with a Pearson correlation of +0.8041 and a Spearman rho of +0.8474. The OLS slope is +24.895 per unit of log1p_trip_distance. The quadratic fit has an R^2 of 0.988, indicating a materially nonlinear relationship. The mean total_amount increases from 17.15 to 90.55 as log1p_trip_distance increases.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>The amount passengers pay for NYC yellow taxi trips is weakly associated with the trip duration per mile, suggesting that longer trips per mile may slightly increase the fare.</t>
+          <t>As the log-transformed trip distance increases, the total amount charged to passengers also increases, suggesting that longer trips are associated with higher fares.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Longer trip durations per mile may reflect traffic congestion, leading to higher fares.</t>
+          <t>Longer distances naturally incur higher fares due to increased time and fuel costs.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>The relationship might be nonlinear, as indicated by the stronger monotonic association.</t>
+          <t>The relationship could be influenced by other fare components that increase with distance.</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Traffic conditions; Time of day; Trip distance</t>
+          <t>Fare components like tolls and surcharges that are distance-dependent.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1333,16 +1333,16 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>very strong</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
@@ -1355,17 +1355,17 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>note:hedged_causal_language; note:filters_not_disclosed</t>
+          <t>note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>2128</v>
+        <v>2455</v>
       </c>
       <c r="V9" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="W9" t="n">
-        <v>2.243</v>
+        <v>2.347</v>
       </c>
     </row>
     <row r="10">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payment_type groups</t>
+          <t>(fare_per_mile / trip_distance)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -1397,42 +1397,42 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>The mean fare amounts for different payment types are: Flex Fare trip ($25.17), Credit card ($19.32), Cash ($19.43), No charge ($19.41), and Dispute ($23.49). The eta squared value of 0.1521 indicates a weak association between payment type and fare amount.</t>
+          <t>The relationship between fare_per_mile_per_trip_distance and total_amount shows a strong inverse association with a Spearman rho of -0.7372. The functional form is inverse, with a fitted curve of y = 19.43 + 15.04/x, achieving an R^2 of 0.983. The Pearson correlation is weakly positive at +0.0406, indicating a negligible linear relationship.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>There is a weak association between the type of payment and the fare amount paid by passengers.</t>
+          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with fare_per_mile_per_trip_distance in a nonlinear manner. As fare_per_mile_per_trip_distance increases, the total amount tends to decrease, but the effect diminishes at higher values.</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Different payment types may be associated with different trip characteristics or passenger preferences.</t>
+          <t>Higher fare_per_mile_per_trip_distance may reflect shorter trips with higher base fares, leading to a lower total amount as distance increases.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>The association might be due to other factors like trip distance or duration that correlate with payment type.</t>
+          <t>The inverse relationship could be due to fixed costs being spread over longer distances, reducing the fare per mile.</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Trip distance; Trip duration; Passenger count</t>
+          <t>Trip distance, trip duration, and fixed surcharges could influence both fare_per_mile_per_trip_distance and total_amount.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>undetermined</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="Q10" t="b">
         <v>1</v>
@@ -1450,21 +1450,21 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>note:accounting_identity_correctly_labelled; note:filters_not_disclosed</t>
+          <t>warning:accounting_identity_presented_as_discovery; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>2136</v>
+        <v>2453</v>
       </c>
       <c r="V10" t="n">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="W10" t="n">
-        <v>2.805</v>
+        <v>3.043</v>
       </c>
     </row>
     <row r="11">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>log1p(trip_distance)</t>
+          <t>fare_per_mile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -1496,27 +1496,27 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between log1p_trip_distance and total_amount, with a Pearson correlation of +0.8041 and a Spearman rho of +0.8474. The OLS slope is +24.895 per unit of log1p_trip_distance. The hexbin plot indicates a dense concentration of data points along the line of best fit, suggesting a strong linear relationship.</t>
+          <t>The relationship between fare_per_mile and total_amount shows a weak positive linear correlation (Pearson r = +0.0405) and a moderate negative monotonic correlation (Spearman rho = -0.4523). The functional form fitted to the conditional mean is inverse, with R^2 = 0.695, indicating a nonlinear relationship. The mean total_amount decreases from 54.58 to 30.81 as fare_per_mile increases.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>This suggests that as the log-transformed trip distance increases, the total amount paid by passengers also increases.</t>
+          <t>The amount passengers pay is weakly associated with fare_per_mile in a nonlinear manner, suggesting that as fare_per_mile increases, the total amount tends to decrease.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Longer trips generally result in higher fares due to increased distance.</t>
+          <t>Higher fare_per_mile values may occur on shorter trips with fixed fees, leading to a higher cost per mile but lower total amounts.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>The relationship may be influenced by other fare components that increase with distance.</t>
+          <t>Airport pickups with fixed fees could inflate fare_per_mile independently of trip length.</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Fare components such as tolls and surcharges that are distance-dependent.</t>
+          <t>Airport pickups; Trip distance</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>very strong</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
@@ -1553,17 +1553,17 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>note:filters_not_disclosed</t>
+          <t>note:accounting_identity_correctly_labelled; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>2166</v>
+        <v>2426</v>
       </c>
       <c r="V11" t="n">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="W11" t="n">
-        <v>1.993</v>
+        <v>2.688</v>
       </c>
     </row>
     <row r="12">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>(trip_distance / passenger_count)</t>
+          <t>trip_duration_minutes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -1595,27 +1595,27 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between trip_distance_per_passenger_count and total_amount, with a Pearson correlation of +0.8452 and a Spearman rho of +0.8337. The OLS slope is +4.4983, indicating that for each unit increase in trip_distance_per_passenger_count, the total_amount increases by approximately $4.50.</t>
+          <t>The statistics show a very strong positive association between trip_duration_minutes and total_amount, with a Pearson correlation of +0.6988 and a Spearman rho of +0.8885. The OLS slope is +1.0388 per unit of trip_duration_minutes. The functional form is linear, with the conditional mean of total_amount increasing from 12.93 to 73.64 as trip_duration_minutes increases.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the trip distance per passenger count. As the distance per passenger increases, the total fare tends to increase.</t>
+          <t>Longer trip durations are associated with higher total amounts paid by passengers.</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Longer trips naturally incur higher fares due to increased distance.; Higher passenger counts may lead to more shared costs, affecting the fare per passenger.</t>
+          <t>Longer trips naturally incur higher fares due to increased time and distance traveled.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>The fare structure inherently ties distance to cost, leading to a mechanical relationship.</t>
+          <t>The total amount is mechanically related to trip duration as it includes time-based fare components.</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Time of day (rush hour conditions); Airport pickups; Traffic conditions</t>
+          <t>Trip distance, as longer durations may also imply longer distances.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>2120</v>
+        <v>2358</v>
       </c>
       <c r="V12" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="W12" t="n">
-        <v>2.115</v>
+        <v>2.741</v>
       </c>
     </row>
     <row r="13">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>(passenger_count * trip_distance)</t>
+          <t>(trip_duration_minutes / tip_fraction_of_fare)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -1694,27 +1694,27 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>The relationship between passenger_count_times_trip_distance and total_amount shows a very strong positive association, with a Pearson correlation of +0.7807 and a Spearman rho of +0.8348. The OLS slope is +2.3402, indicating that for each unit increase in passenger_count_times_trip_distance, the total_amount increases by approximately 2.34 USD. The cross-fold stability is 0.997, indicating consistent results across different data subsets.</t>
+          <t>The relationship between trip_duration_minutes_per_tip_fraction_of_fare and total_amount is positive and very strong, with a Spearman rho of +0.8097. The relationship is nonlinear, best described by a quadratic function with an R^2 of 0.990. The total_amount increases with trip_duration_minutes_per_tip_fraction_of_fare, but the rate of increase slows down as the value of x increases, saturating near a turning point of x = 320.7.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the combined effect of the number of passengers and the trip distance.</t>
+          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the derived feature trip_duration_minutes_per_tip_fraction_of_fare. As this feature increases, the total fare also increases, but at a decreasing rate.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Longer distances and more passengers likely increase the fare due to higher base fare and distance charges.</t>
+          <t>Longer trips with higher tip fractions may indicate more expensive rides, leading to higher total fares.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>The fare structure inherently includes distance and passenger count, leading to a mechanical relationship.</t>
+          <t>The derived feature may capture other underlying factors such as traffic conditions or passenger behavior that influence fare.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Trip duration and traffic conditions could also affect the total fare.</t>
+          <t>Trip distance and duration, as they are components of the derived feature and directly affect fare.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1734,11 +1734,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>explained</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0.99</v>
+        <v>0.84</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -1747,21 +1747,21 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>note:hedged_causal_language</t>
+          <t>warning:accounting_identity_presented_as_discovery; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>2138</v>
+        <v>2467</v>
       </c>
       <c r="V13" t="n">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="W13" t="n">
-        <v>2.294</v>
+        <v>3.266</v>
       </c>
     </row>
     <row r="14">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(passenger_count / trip_distance)</t>
+          <t>is_airport_pickup groups</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>box</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1793,51 +1793,51 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>The relationship between passenger_count_per_trip_distance and total_amount shows a very strong negative monotonic association (Spearman rho = -0.8213) and a weaker negative linear association (Pearson r = -0.1591). The OLS slope is -1.2715 per unit of passenger_count_per_trip_distance.</t>
+          <t>The mean total amount for non-airport pickups (is_airport_pickup=0.0) is $24.36, while for airport pickups (is_airport_pickup=1.0) it is $75.37. The eta squared value is 0.6426, indicating a strong variance explained by the group.</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>As the passenger_count_per_trip_distance increases, the total amount paid tends to decrease.</t>
+          <t>The total amount passengers pay for NYC yellow taxi trips is strongly associated with whether the pickup is at an airport.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Higher passenger count per mile might indicate shorter trips with more passengers, leading to lower total fares.</t>
+          <t>Airport pickups may include additional fees and longer distances, contributing to higher total amounts.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Nonlinear pricing structures or discounts for shared rides could affect the total amount.</t>
+          <t>Trips from airports might inherently be longer, leading to higher fares.</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Trip distance; Trip duration; Fare components like tolls and surcharges</t>
+          <t>Trip distance, time of day, and traffic conditions could also influence the total amount.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>very strong</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>mechanical</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>note:filters_not_disclosed; note:semantically_surprising</t>
+          <t>note:accounting_identity_correctly_labelled; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>2156</v>
+        <v>2185</v>
       </c>
       <c r="V14" t="n">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="W14" t="n">
-        <v>2.066</v>
+        <v>3.022</v>
       </c>
     </row>
     <row r="15">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>log(trip_duration_minutes)</t>
+          <t>RatecodeID groups</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>box</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -1892,42 +1892,42 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>The statistics show a very strong positive association between log_trip_duration_minutes and total_amount, with a Pearson correlation of +0.6849 and a Spearman rho of +0.8885. The OLS slope is +19.826 per unit of log_trip_duration_minutes.</t>
+          <t>The RatecodeID is strongly associated with the total_amount passengers pay for NYC yellow taxi trips, with an eta squared of 0.6788. The group means show that trips with RatecodeID 4 (Nassau or Westchester) have the highest mean total amount ($135.6), while RatecodeID 6 (Group ride) has the lowest ($4.5).</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>As the log of trip duration increases, the total amount passengers pay tends to increase.</t>
+          <t>Different rate codes are associated with varying fare amounts, indicating that the type of trip (e.g., airport, negotiated fare) influences the total fare.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Longer trips naturally incur higher fares due to increased time and distance traveled.</t>
+          <t>Rate codes 2 and 3 are flat/administered fares, which may result in higher average fares due to fixed pricing for airport trips.; RatecodeID 4 trips may involve longer distances or higher tolls, leading to higher total amounts.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>The relationship could be influenced by other factors such as traffic conditions or route efficiency.</t>
+          <t>The presence of flat fares for certain rate codes could skew the average total amounts.; RatecodeID 99 (Null/unknown) may include a mix of different trip types, affecting its average.</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Trip distance, as longer distances typically result in longer durations and higher fares.</t>
+          <t>Trip distance and duration, which are not directly accounted for in flat/administered fares.; Passenger count, which can influence the total fare through shared rides.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>undetermined</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>very strong</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.849</v>
+        <v>0.9</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
@@ -1945,120 +1945,21 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>warning:causal_claim_from_association; note:filters_not_disclosed</t>
+          <t>note:hedged_causal_language; note:filters_not_disclosed</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>2141</v>
+        <v>2364</v>
       </c>
       <c r="V15" t="n">
-        <v>236</v>
+        <v>355</v>
       </c>
       <c r="W15" t="n">
-        <v>2.084</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>(passenger_count * trip_duration_minutes)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>hexbin</t>
-        </is>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>gpt-4o-2024-08-06</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>The data shows a very strong positive association between passenger_count_times_trip_duration_minutes and total_amount, with a Pearson correlation of +0.6343 and a Spearman rho of +0.8389. The OLS slope is +0.61356 per unit of passenger_count_times_trip_duration_minutes.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>The amount passengers pay for NYC yellow taxi trips is strongly associated with the interaction of passenger count and trip duration.</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Longer trips with more passengers may naturally result in higher fares due to increased time and distance.; Taxi fare structures often include components that increase with time and distance.</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>The correlation could be influenced by other fare components that are not directly related to passenger count or trip duration.</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>Trip distance; Fare components such as tolls and surcharges</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>positive</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>very strong</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>explained</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>note:hedged_causal_language; note:filters_not_disclosed</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>2124</v>
-      </c>
-      <c r="V16" t="n">
-        <v>271</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.253</v>
+        <v>3.369</v>
       </c>
     </row>
   </sheetData>
